--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -273,7 +273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q53"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="12"/>
     <col min="2" max="2" customWidth="1" width="28"/>
@@ -2803,7 +2803,7 @@
         <v>—</v>
       </c>
       <c r="G48" t="str">
-        <v>Cover page.jpg</v>
+        <v>cover page new.png</v>
       </c>
       <c r="H48" t="str">
         <v>02.08.2026</v>
@@ -2833,14 +2833,274 @@
         <v>Yes</v>
       </c>
       <c r="Q48" t="str">
-        <v>Confirmed official magazine title: একই শিকড়. Source SHA-256: d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7.</v>
-      </c>
-    </row>
-    <row r="49" ht="22.05" customHeight="1"/>
-    <row r="50" ht="22.05" customHeight="1"/>
-    <row r="51" ht="22.05" customHeight="1"/>
-    <row r="52" ht="22.05" customHeight="1"/>
-    <row r="53" ht="22.05" customHeight="1"/>
+        <v>Confirmed official magazine title: একই শিকড়. Source SHA-256: d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7. Sprint v2: cover replaced with "cover page new.png" (SHA-256 29a12bcbb8baca83a76e6bd6eee546471d7ece7f5d04a37468e4e5234f53d327). Previous source preserved unchanged as "Cover page.jpg" (SHA-256 d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7).</v>
+      </c>
+    </row>
+    <row r="49" ht="22.05" customHeight="1">
+      <c r="A49" t="str">
+        <v>20</v>
+      </c>
+      <c r="B49" t="str">
+        <v xml:space="preserve">Climate Change and its Impact on Amchi Mumbai </v>
+      </c>
+      <c r="C49" t="str">
+        <v>Technical Article</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Sudipta Chakraborty</v>
+      </c>
+      <c r="E49" t="str">
+        <v>1978</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Article for BECAA Maharashtra Souveneir.pdf</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Technical Articles</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="22.05" customHeight="1">
+      <c r="A50" t="str">
+        <v>21</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Chatgpt</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Painting / Drawing</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Kallol Roy</v>
+      </c>
+      <c r="E50" t="str">
+        <v>1991</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="G50" t="str">
+        <v>chatgpt kallol.jpeg</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Paintings / Drawings</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="22.05" customHeight="1">
+      <c r="A51" t="str">
+        <v>22</v>
+      </c>
+      <c r="B51" t="str">
+        <v>গোলাপ</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Poem</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Shubhra Basu (wife of Pranab Basu)</v>
+      </c>
+      <c r="E51" t="str">
+        <v>1978</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Shubhra Basu.docx</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Stories / Literature</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="22.05" customHeight="1">
+      <c r="A52" t="str">
+        <v>23</v>
+      </c>
+      <c r="B52" t="str">
+        <v xml:space="preserve">বেঁচে থাকার লড়াই ও স্বপ্নের পথ </v>
+      </c>
+      <c r="C52" t="str">
+        <v>Article</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Palash Biswas</v>
+      </c>
+      <c r="E52" t="str">
+        <v>2006</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Palash Article.docx</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K52" t="str">
+        <v>College Memories</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="22.05" customHeight="1">
+      <c r="A53" t="str">
+        <v>24</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Siddhartha Mukhopadhyay story</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Story</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Siddhartha Mukhopadhyay</v>
+      </c>
+      <c r="E53" t="str">
+        <v>1986</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Electrical</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Siddhartha Mukhopadhyay story.docx</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Awaiting</v>
+      </c>
+      <c r="K53" t="str">
+        <v>College Memories</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="54" ht="22.05" customHeight="1"/>
     <row r="55" ht="22.05" customHeight="1"/>
     <row r="56" ht="22.05" customHeight="1"/>
@@ -2890,7 +3150,7 @@
     <row r="100" ht="22.05" customHeight="1"/>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q53"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -2865,7 +2865,7 @@
         <v>Print and web</v>
       </c>
       <c r="J49" t="str">
-        <v>Approved</v>
+        <v>Excluded – Source file not received</v>
       </c>
       <c r="K49" t="str">
         <v>Technical Articles</v>
@@ -2874,7 +2874,7 @@
         <v/>
       </c>
       <c r="M49" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N49" t="str">
         <v/>
@@ -2883,10 +2883,10 @@
         <v/>
       </c>
       <c r="P49" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="Q49" t="str">
-        <v/>
+        <v>Sprint v2: named source file "Article for BECAA Maharashtra Souveneir.pdf" was not found in v2-incoming or anywhere else in the project. Distinct from the already-published ART-006 source ("Article for BECAA Maharashtra Souvenir.docx", a different author). Excluded pending the correct file or an editorial correction of this row. See sprints/v2/MATERIAL_CHANGE_REGISTER.md.</v>
       </c>
     </row>
     <row r="50" ht="22.05" customHeight="1">
@@ -3077,7 +3077,7 @@
         <v>Pending</v>
       </c>
       <c r="J53" t="str">
-        <v>Awaiting</v>
+        <v>Excluded – Content and permission pending</v>
       </c>
       <c r="K53" t="str">
         <v>College Memories</v>
@@ -3086,7 +3086,7 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N53" t="str">
         <v/>
@@ -3095,10 +3095,10 @@
         <v/>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="Q53" t="str">
-        <v/>
+        <v>Sprint v2: source docx contains only placeholder text ("Story upcoming.") and Permission is still Pending. Excluded until real content and permission are both received. See sprints/v2/MATERIAL_CHANGE_REGISTER.md.</v>
       </c>
     </row>
     <row r="54" ht="22.05" customHeight="1"/>

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -1357,7 +1357,7 @@
         <v>ADV-001</v>
       </c>
       <c r="B21" t="str">
-        <v>Skylark Advertisement</v>
+        <v>With best compliments from Skylark</v>
       </c>
       <c r="C21" t="str">
         <v>Advertisement</v>
@@ -1402,7 +1402,7 @@
         <v>Yes</v>
       </c>
       <c r="Q21" t="str">
-        <v>Preferred artwork: 1 Skylark.png. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 1 Skylark.png. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1">
@@ -1410,7 +1410,7 @@
         <v>ADV-002</v>
       </c>
       <c r="B22" t="str">
-        <v>PNB Housing Advertisement</v>
+        <v>With best compliments from PNB Housing</v>
       </c>
       <c r="C22" t="str">
         <v>Advertisement</v>
@@ -1455,7 +1455,7 @@
         <v>Yes</v>
       </c>
       <c r="Q22" t="str">
-        <v>Preferred artwork: 2 d PNB FD Magazine AD_A4-01.pdf. Selected full-page A4 file explicitly named Magazine AD; other PNB files are alternate designs/logo.</v>
+        <v>Preferred artwork: 2 d PNB FD Magazine AD_A4-01.pdf. Selected full-page A4 file explicitly named Magazine AD; other PNB files are alternate designs/logo. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1">
@@ -1463,7 +1463,7 @@
         <v>ADV-003</v>
       </c>
       <c r="B23" t="str">
-        <v>Vistaar Finance Advertisement</v>
+        <v>With best compliments from Vistaar Finance</v>
       </c>
       <c r="C23" t="str">
         <v>Advertisement</v>
@@ -1508,7 +1508,7 @@
         <v>Yes</v>
       </c>
       <c r="Q23" t="str">
-        <v>Preferred artwork: 3 Vistaar Finance.jpg. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 3 Vistaar Finance.jpg. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1">
@@ -1516,7 +1516,7 @@
         <v>ADV-004</v>
       </c>
       <c r="B24" t="str">
-        <v>Gainwell Technologies Advertisement</v>
+        <v>With best compliments from Gainwell Technologies</v>
       </c>
       <c r="C24" t="str">
         <v>Advertisement</v>
@@ -1561,7 +1561,7 @@
         <v>Yes</v>
       </c>
       <c r="Q24" t="str">
-        <v>Preferred artwork: 4 Gainwell Technologies.jpg. Selected primary company artwork; CAT image is supplemental alternate artwork.</v>
+        <v>Preferred artwork: 4 Gainwell Technologies.jpg. Selected primary company artwork; CAT image is supplemental alternate artwork. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1">
@@ -1569,7 +1569,7 @@
         <v>ADV-005</v>
       </c>
       <c r="B25" t="str">
-        <v>Tata Capital Ltd. Retail Finance Advertisement</v>
+        <v>With best compliments from Tata Capital Ltd. (Retail Finance)</v>
       </c>
       <c r="C25" t="str">
         <v>Advertisement</v>
@@ -1614,7 +1614,7 @@
         <v>Yes</v>
       </c>
       <c r="Q25" t="str">
-        <v>Preferred artwork: 5a Tata Capital ltd. (Retail Finance).jpg. Selected full-page retail-finance artwork; base file is logo-only.</v>
+        <v>Preferred artwork: 5a Tata Capital ltd. (Retail Finance).jpg. Selected full-page retail-finance artwork; base file is logo-only. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1">
@@ -1622,7 +1622,7 @@
         <v>ADV-006</v>
       </c>
       <c r="B26" t="str">
-        <v>Tata Capital Housing Finance Ltd. Advertisement</v>
+        <v>With best compliments from Tata Capital Housing Finance Ltd.</v>
       </c>
       <c r="C26" t="str">
         <v>Advertisement</v>
@@ -1667,7 +1667,7 @@
         <v>Yes</v>
       </c>
       <c r="Q26" t="str">
-        <v>Preferred artwork: 6 d tata capital.pdf. Selected full portrait PDF advertisement; JPG files are alternate banners/placements.</v>
+        <v>Preferred artwork: 6 d tata capital.pdf. Selected full portrait PDF advertisement; JPG files are alternate banners/placements. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="27" ht="22.05" customHeight="1">
@@ -1675,7 +1675,7 @@
         <v>ADV-007</v>
       </c>
       <c r="B27" t="str">
-        <v>OnShore Construction Pvt Ltd Advertisement</v>
+        <v>With best compliments from OnShore Construction Pvt Ltd</v>
       </c>
       <c r="C27" t="str">
         <v>Advertisement</v>
@@ -1720,7 +1720,7 @@
         <v>Yes</v>
       </c>
       <c r="Q27" t="str">
-        <v>Preferred artwork: 7 OnShore Construction Pvt Ltd .png. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 7 OnShore Construction Pvt Ltd .png. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="28" ht="22.05" customHeight="1">
@@ -1728,7 +1728,7 @@
         <v>ADV-008</v>
       </c>
       <c r="B28" t="str">
-        <v>Roofs &amp; Ceilings Advertisement</v>
+        <v>With best compliments from Roofs &amp; Ceilings</v>
       </c>
       <c r="C28" t="str">
         <v>Advertisement</v>
@@ -1773,7 +1773,7 @@
         <v>Yes</v>
       </c>
       <c r="Q28" t="str">
-        <v>Preferred artwork: 8 Roofs &amp; Ceilings.png. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 8 Roofs &amp; Ceilings.png. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="29" ht="22.05" customHeight="1">
@@ -1834,7 +1834,7 @@
         <v>ADV-010</v>
       </c>
       <c r="B30" t="str">
-        <v>Indus Grand Advertisement</v>
+        <v>With best compliments from Indus Grand</v>
       </c>
       <c r="C30" t="str">
         <v>Advertisement</v>
@@ -1879,7 +1879,7 @@
         <v>Yes</v>
       </c>
       <c r="Q30" t="str">
-        <v>Preferred artwork: 10 Indus Grand.jpeg. Selected full advertisement; 10a is logo-only.</v>
+        <v>Preferred artwork: 10 Indus Grand.jpeg. Selected full advertisement; 10a is logo-only. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="31" ht="22.05" customHeight="1">
@@ -1887,7 +1887,7 @@
         <v>ADV-011</v>
       </c>
       <c r="B31" t="str">
-        <v>Axelon Advertisement</v>
+        <v>With best compliments from Axelon</v>
       </c>
       <c r="C31" t="str">
         <v>Advertisement</v>
@@ -1932,7 +1932,7 @@
         <v>Yes</v>
       </c>
       <c r="Q31" t="str">
-        <v>Preferred artwork: 11 Axelon.jpg. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 11 Axelon.jpg. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="32" ht="22.05" customHeight="1">
@@ -1940,7 +1940,7 @@
         <v>ADV-012</v>
       </c>
       <c r="B32" t="str">
-        <v>Aarvi Encon Advertisement</v>
+        <v>With best compliments from Aarvi Encon</v>
       </c>
       <c r="C32" t="str">
         <v>Advertisement</v>
@@ -1985,7 +1985,7 @@
         <v>Yes</v>
       </c>
       <c r="Q32" t="str">
-        <v>Preferred artwork: 12 arvi enercon.jpeg. Exact tracker file exists; artwork and sponsor workbook confirm Aarvi Encon despite filename spelling.</v>
+        <v>Preferred artwork: 12 arvi enercon.jpeg. Exact tracker file exists; artwork and sponsor workbook confirm Aarvi Encon despite filename spelling. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="33" ht="22.05" customHeight="1">
@@ -1993,7 +1993,7 @@
         <v>ADV-013</v>
       </c>
       <c r="B33" t="str">
-        <v>Anand Rathi Advertisement</v>
+        <v>With best compliments from Anand Rathi</v>
       </c>
       <c r="C33" t="str">
         <v>Advertisement</v>
@@ -2038,7 +2038,7 @@
         <v>Yes</v>
       </c>
       <c r="Q33" t="str">
-        <v>Preferred artwork: 13a Anand Rathi.jpeg. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 13a Anand Rathi.jpeg. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="34" ht="22.05" customHeight="1">
@@ -2046,7 +2046,7 @@
         <v>ADV-014</v>
       </c>
       <c r="B34" t="str">
-        <v>Future Netwings Solutions Advertisement</v>
+        <v>With best compliments from Future Netwings Solutions</v>
       </c>
       <c r="C34" t="str">
         <v>Advertisement</v>
@@ -2091,7 +2091,7 @@
         <v>Yes</v>
       </c>
       <c r="Q34" t="str">
-        <v>Preferred artwork: 14 a future netwings.pdf. Selected full-page PDF; PNG files are logo/raster derivative alternatives.</v>
+        <v>Preferred artwork: 14 a future netwings.pdf. Selected full-page PDF; PNG files are logo/raster derivative alternatives. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="35" ht="22.05" customHeight="1">
@@ -2099,7 +2099,7 @@
         <v>ADV-015</v>
       </c>
       <c r="B35" t="str">
-        <v>Swaraj Shoes Advertisement</v>
+        <v>With best compliments from Swaraj Shoes</v>
       </c>
       <c r="C35" t="str">
         <v>Advertisement</v>
@@ -2144,7 +2144,7 @@
         <v>Yes</v>
       </c>
       <c r="Q35" t="str">
-        <v>Preferred artwork: 15 Swaraj Shoes.jpeg. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 15 Swaraj Shoes.jpeg. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="36" ht="22.05" customHeight="1">
@@ -2205,7 +2205,7 @@
         <v>ADV-017</v>
       </c>
       <c r="B37" t="str">
-        <v>UREDCONNECT Advertisement</v>
+        <v>With best compliments from UREDCONNECT</v>
       </c>
       <c r="C37" t="str">
         <v>Advertisement</v>
@@ -2250,7 +2250,7 @@
         <v>Yes</v>
       </c>
       <c r="Q37" t="str">
-        <v>Preferred artwork: 17 UREDCONNECT.jpeg. Selected primary numbered advertisement; 17a is an alternate design.</v>
+        <v>Preferred artwork: 17 UREDCONNECT.jpeg. Selected primary numbered advertisement; 17a is an alternate design. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="38" ht="22.05" customHeight="1">
@@ -2258,7 +2258,7 @@
         <v>ADV-018</v>
       </c>
       <c r="B38" t="str">
-        <v>Eframe Advertisement</v>
+        <v>With best compliments from Eframe</v>
       </c>
       <c r="C38" t="str">
         <v>Advertisement</v>
@@ -2303,7 +2303,7 @@
         <v>Yes</v>
       </c>
       <c r="Q38" t="str">
-        <v>Preferred artwork: 18 Eframe.jpeg. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 18 Eframe.jpeg. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="39" ht="22.05" customHeight="1">
@@ -2311,7 +2311,7 @@
         <v>ADV-019</v>
       </c>
       <c r="B39" t="str">
-        <v>Network Techlabs Advertisement</v>
+        <v>With best compliments from Network Techlabs</v>
       </c>
       <c r="C39" t="str">
         <v>Advertisement</v>
@@ -2356,7 +2356,7 @@
         <v>Yes</v>
       </c>
       <c r="Q39" t="str">
-        <v>Preferred artwork: 19 Network Techlabs.png. Selected primary numbered artwork; 19A is an alternate banner.</v>
+        <v>Preferred artwork: 19 Network Techlabs.png. Selected primary numbered artwork; 19A is an alternate banner. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="40" ht="22.05" customHeight="1">
@@ -2364,7 +2364,7 @@
         <v>ADV-020</v>
       </c>
       <c r="B40" t="str">
-        <v>Schnelltech Global Advertisement</v>
+        <v>With best compliments from Schnelltech Global</v>
       </c>
       <c r="C40" t="str">
         <v>Advertisement</v>
@@ -2409,7 +2409,7 @@
         <v>Yes</v>
       </c>
       <c r="Q40" t="str">
-        <v>Preferred artwork: 20 b Schnelltech Global.pdf. Selected full magazine PDF; base file is logo-only and 20a is a raster derivative.</v>
+        <v>Preferred artwork: 20 b Schnelltech Global.pdf. Selected full magazine PDF; base file is logo-only and 20a is a raster derivative. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="41" ht="22.05" customHeight="1">
@@ -2417,7 +2417,7 @@
         <v>ADV-021</v>
       </c>
       <c r="B41" t="str">
-        <v>Bhavik Advertisement</v>
+        <v>With best compliments from Bhavik</v>
       </c>
       <c r="C41" t="str">
         <v>Advertisement</v>
@@ -2462,7 +2462,7 @@
         <v>Yes</v>
       </c>
       <c r="Q41" t="str">
-        <v>Preferred artwork: 21 Bhavik.jpeg. Company name corrected to Bhavik from the name displayed in the approved artwork, per user authorization.</v>
+        <v>Preferred artwork: 21 Bhavik.jpeg. Company name corrected to Bhavik from the name displayed in the approved artwork, per user authorization. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="42" ht="22.05" customHeight="1">
@@ -2470,7 +2470,7 @@
         <v>ADV-022</v>
       </c>
       <c r="B42" t="str">
-        <v>Pratap Caterer Advertisement</v>
+        <v>With best compliments from Pratap Caterer</v>
       </c>
       <c r="C42" t="str">
         <v>Advertisement</v>
@@ -2515,7 +2515,7 @@
         <v>Yes</v>
       </c>
       <c r="Q42" t="str">
-        <v>Preferred artwork: 22 pratap caterer.png. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 22 pratap caterer.png. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="43" ht="22.05" customHeight="1">
@@ -2523,7 +2523,7 @@
         <v>ADV-023</v>
       </c>
       <c r="B43" t="str">
-        <v>Clover Blakefield Reality LLP Advertisement</v>
+        <v>With best compliments from Clover Blakefield Reality LLP</v>
       </c>
       <c r="C43" t="str">
         <v>Advertisement</v>
@@ -2568,7 +2568,7 @@
         <v>Yes</v>
       </c>
       <c r="Q43" t="str">
-        <v>Preferred artwork: 23 Clover Blakefield Reality LLP.png. Exact available artwork matched to tracker row.</v>
+        <v>Preferred artwork: 23 Clover Blakefield Reality LLP.png. Exact available artwork matched to tracker row. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="44" ht="22.05" customHeight="1">
@@ -2682,7 +2682,7 @@
         <v>ADV-026</v>
       </c>
       <c r="B46" t="str">
-        <v>CETEST Advertisement</v>
+        <v>With best compliments from CETEST</v>
       </c>
       <c r="C46" t="str">
         <v>Advertisement</v>
@@ -2727,7 +2727,7 @@
         <v>Yes</v>
       </c>
       <c r="Q46" t="str">
-        <v>Explicitly approved for 2026 review publication. Render slide 1 from the original PPTX with LibreOffice Impress PDF export, then rasterize at 300 DPI; preserve original PPTX untouched.</v>
+        <v>Explicitly approved for 2026 review publication. Render slide 1 from the original PPTX with LibreOffice Impress PDF export, then rasterize at 300 DPI; preserve original PPTX untouched. Sprint v3 (2026-09-14): public display title changed to "With best compliments from [Company]" per sprints/v3/PRD.md §4.3; artwork, source file and normalized files unchanged.</v>
       </c>
     </row>
     <row r="47" ht="22.05" customHeight="1">

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -1296,7 +1296,7 @@
         <v>Yes</v>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>Sprint v3: revised source received 2026-09-14 (SHA-256 ed3fd766…) replaces the 01.08.2026 version (SHA-256 df446f44…), preserved in 04_MAGAZINE_WORKING/SUPERSEDED_SOURCES/2026-09-14/ and git history.</v>
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1">
@@ -3053,7 +3053,7 @@
         <v>24</v>
       </c>
       <c r="B53" t="str">
-        <v>Siddhartha Mukhopadhyay story</v>
+        <v>প্যাঁড়া (Siddhartha Mukhopadhyay story)</v>
       </c>
       <c r="C53" t="str">
         <v>Story</v>
@@ -3071,13 +3071,13 @@
         <v>Siddhartha Mukhopadhyay story.docx</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>14.09.2026</v>
       </c>
       <c r="I53" t="str">
-        <v>Pending</v>
+        <v>Print and web</v>
       </c>
       <c r="J53" t="str">
-        <v>Excluded – Content and permission pending</v>
+        <v>Approved</v>
       </c>
       <c r="K53" t="str">
         <v>College Memories</v>
@@ -3086,7 +3086,7 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N53" t="str">
         <v/>
@@ -3095,10 +3095,10 @@
         <v/>
       </c>
       <c r="P53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="Q53" t="str">
-        <v>Sprint v2: source docx contains only placeholder text ("Story upcoming.") and Permission is still Pending. Excluded until real content and permission are both received. See sprints/v2/MATERIAL_CHANGE_REGISTER.md.</v>
+        <v>Sprint v2: source docx contains only placeholder text ("Story upcoming.") and Permission is still Pending. Excluded until real content and permission are both received. See sprints/v2/MATERIAL_CHANGE_REGISTER.md. Sprint v3: real content received and approval confirmed 2026-09-14; published as ART-012.</v>
       </c>
     </row>
     <row r="54" ht="22.05" customHeight="1"/>

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -273,7 +273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q55"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="12"/>
     <col min="2" max="2" customWidth="1" width="28"/>
@@ -2735,13 +2735,13 @@
         <v>ADV-027</v>
       </c>
       <c r="B47" t="str">
-        <v>Aniket Pal Advertisement</v>
+        <v>Best Compliment from Sarc Epic</v>
       </c>
       <c r="C47" t="str">
         <v>Advertisement</v>
       </c>
       <c r="D47" t="str">
-        <v>Aniket Pal (company name unavailable)</v>
+        <v>Sarc Epic</v>
       </c>
       <c r="E47" t="str">
         <v>—</v>
@@ -2753,13 +2753,13 @@
         <v>—</v>
       </c>
       <c r="H47" t="str">
-        <v>—</v>
+        <v>15.09.2026</v>
       </c>
       <c r="I47" t="str">
         <v>Print and web</v>
       </c>
       <c r="J47" t="str">
-        <v>Excluded – Source artwork not available</v>
+        <v>Approved</v>
       </c>
       <c r="K47" t="str">
         <v>Advertisements</v>
@@ -2768,33 +2768,33 @@
         <v>—</v>
       </c>
       <c r="M47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N47" t="str">
         <v>—</v>
       </c>
       <c r="O47" t="str">
-        <v>Source: Debojit Dutta Biswas. Sponsor sheet states that the company name is unavailable. No matching file is visible in the screenshots.</v>
+        <v>Sprint v4: company name confirmed as Sarc Epic (same sponsor as the previously excluded "Aniket Pal" entry, source via Debojit da). Text-only advertisement; no source artwork supplied. Source: AniketPal (Debojit da).</v>
       </c>
       <c r="P47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="Q47" t="str">
-        <v>Confirmed excluded from website, print and Sponsor Acknowledgements: company name incomplete or unavailable.</v>
+        <v>Confirmed excluded from website, print and Sponsor Acknowledgements: company name incomplete or unavailable. Sprint v4: re-included as ADV-027, Approved, Sarc Epic — see Notes.</v>
       </c>
     </row>
     <row r="48" ht="22.05" customHeight="1">
       <c r="A48" t="str">
-        <v>COV-001</v>
+        <v>ADV-028</v>
       </c>
       <c r="B48" t="str">
-        <v>একই শিকড় — Official Cover</v>
+        <v>Best Compliment from M/s Balajee Infrate</v>
       </c>
       <c r="C48" t="str">
-        <v>Cover</v>
+        <v>Advertisement</v>
       </c>
       <c r="D48" t="str">
-        <v>BECAA Maharashtra</v>
+        <v>M/s Balajee Infrate</v>
       </c>
       <c r="E48" t="str">
         <v>—</v>
@@ -2803,10 +2803,10 @@
         <v>—</v>
       </c>
       <c r="G48" t="str">
-        <v>cover page new.png</v>
+        <v>—</v>
       </c>
       <c r="H48" t="str">
-        <v>02.08.2026</v>
+        <v>15.09.2026</v>
       </c>
       <c r="I48" t="str">
         <v>Print and web</v>
@@ -2815,10 +2815,10 @@
         <v>Approved</v>
       </c>
       <c r="K48" t="str">
-        <v>Front Cover</v>
+        <v>Advertisements</v>
       </c>
       <c r="L48" t="str">
-        <v>1</v>
+        <v>—</v>
       </c>
       <c r="M48" t="str">
         <v>Yes</v>
@@ -2827,92 +2827,92 @@
         <v>—</v>
       </c>
       <c r="O48" t="str">
-        <v>Official 2026 magazine cover supplied in incoming content. Preserve exactly; do not edit, crop, regenerate or alter the Bengali title.</v>
+        <v>Text-only advertisement; no source artwork supplied. Source: Keya Mukhopadhya. Intended for magazine printing.</v>
       </c>
       <c r="P48" t="str">
         <v>Yes</v>
       </c>
       <c r="Q48" t="str">
-        <v>Confirmed official magazine title: একই শিকড়. Source SHA-256: d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7. Sprint v2: cover replaced with "cover page new.png" (SHA-256 29a12bcbb8baca83a76e6bd6eee546471d7ece7f5d04a37468e4e5234f53d327). Previous source preserved unchanged as "Cover page.jpg" (SHA-256 d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7).</v>
+        <v>Sprint v4: new text-only advertisement, published as ADV-028.</v>
       </c>
     </row>
     <row r="49" ht="22.05" customHeight="1">
       <c r="A49" t="str">
-        <v>20</v>
+        <v>ADV-029</v>
       </c>
       <c r="B49" t="str">
-        <v xml:space="preserve">Climate Change and its Impact on Amchi Mumbai </v>
+        <v>In fond memory of Late Shri Bhakta Mohon Mitra</v>
       </c>
       <c r="C49" t="str">
-        <v>Technical Article</v>
+        <v>Advertisement</v>
       </c>
       <c r="D49" t="str">
-        <v>Sudipta Chakraborty</v>
+        <v>Subrata Mitra (son), Soma Mitra (daughter)</v>
       </c>
       <c r="E49" t="str">
-        <v>1978</v>
+        <v>—</v>
       </c>
       <c r="F49" t="str">
-        <v>Civil</v>
+        <v>—</v>
       </c>
       <c r="G49" t="str">
-        <v>Article for BECAA Maharashtra Souveneir.pdf</v>
+        <v>Supriyo.JPG</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>15.09.2026</v>
       </c>
       <c r="I49" t="str">
         <v>Print and web</v>
       </c>
       <c r="J49" t="str">
-        <v>Excluded – Source file not received</v>
+        <v>Approved</v>
       </c>
       <c r="K49" t="str">
-        <v>Technical Articles</v>
+        <v>Advertisements</v>
       </c>
       <c r="L49" t="str">
-        <v/>
+        <v>—</v>
       </c>
       <c r="M49" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>—</v>
       </c>
       <c r="O49" t="str">
-        <v/>
+        <v>Memorial contribution sponsored by the son and daughter; not a company advertisement. Source: SUPRIO CHOUDHURY.</v>
       </c>
       <c r="P49" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="Q49" t="str">
-        <v>Sprint v2: named source file "Article for BECAA Maharashtra Souveneir.pdf" was not found in v2-incoming or anywhere else in the project. Distinct from the already-published ART-006 source ("Article for BECAA Maharashtra Souvenir.docx", a different author). Excluded pending the correct file or an editorial correction of this row. See sprints/v2/MATERIAL_CHANGE_REGISTER.md.</v>
+        <v>Sprint v4: new memorial contribution, published as ADV-029.</v>
       </c>
     </row>
     <row r="50" ht="22.05" customHeight="1">
       <c r="A50" t="str">
-        <v>21</v>
+        <v>COV-001</v>
       </c>
       <c r="B50" t="str">
-        <v>Chatgpt</v>
+        <v>একই শিকড় — Official Cover</v>
       </c>
       <c r="C50" t="str">
-        <v>Painting / Drawing</v>
+        <v>Cover</v>
       </c>
       <c r="D50" t="str">
-        <v>Kallol Roy</v>
+        <v>BECAA Maharashtra</v>
       </c>
       <c r="E50" t="str">
-        <v>1991</v>
+        <v>—</v>
       </c>
       <c r="F50" t="str">
-        <v>Civil</v>
+        <v>—</v>
       </c>
       <c r="G50" t="str">
-        <v>chatgpt kallol.jpeg</v>
+        <v>cover page new.png</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>02.08.2026</v>
       </c>
       <c r="I50" t="str">
         <v>Print and web</v>
@@ -2921,39 +2921,39 @@
         <v>Approved</v>
       </c>
       <c r="K50" t="str">
-        <v>Paintings / Drawings</v>
+        <v>Front Cover</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="M50" t="str">
         <v>Yes</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>—</v>
       </c>
       <c r="O50" t="str">
-        <v/>
+        <v>Official 2026 magazine cover supplied in incoming content. Preserve exactly; do not edit, crop, regenerate or alter the Bengali title.</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q50" t="str">
-        <v/>
+        <v>Confirmed official magazine title: একই শিকড়. Source SHA-256: d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7. Sprint v2: cover replaced with "cover page new.png" (SHA-256 29a12bcbb8baca83a76e6bd6eee546471d7ece7f5d04a37468e4e5234f53d327). Previous source preserved unchanged as "Cover page.jpg" (SHA-256 d8dfb14bf8aeb93bedd74fabdd884ab51e1a433cda37c2210125a0b5f315d8e7).</v>
       </c>
     </row>
     <row r="51" ht="22.05" customHeight="1">
       <c r="A51" t="str">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B51" t="str">
-        <v>গোলাপ</v>
+        <v xml:space="preserve">Climate Change and its Impact on Amchi Mumbai </v>
       </c>
       <c r="C51" t="str">
-        <v>Poem</v>
+        <v>Technical Article</v>
       </c>
       <c r="D51" t="str">
-        <v>Shubhra Basu (wife of Pranab Basu)</v>
+        <v>Sudipta Chakraborty</v>
       </c>
       <c r="E51" t="str">
         <v>1978</v>
@@ -2962,7 +2962,7 @@
         <v>Civil</v>
       </c>
       <c r="G51" t="str">
-        <v>Shubhra Basu.docx</v>
+        <v>Article for BECAA Maharashtra Souveneir.pdf</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -2971,16 +2971,16 @@
         <v>Print and web</v>
       </c>
       <c r="J51" t="str">
-        <v>Approved</v>
+        <v>Excluded – Source file not received</v>
       </c>
       <c r="K51" t="str">
-        <v>Stories / Literature</v>
+        <v>Technical Articles</v>
       </c>
       <c r="L51" t="str">
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N51" t="str">
         <v/>
@@ -2989,33 +2989,33 @@
         <v/>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="Q51" t="str">
-        <v/>
+        <v>Sprint v2: named source file "Article for BECAA Maharashtra Souveneir.pdf" was not found in v2-incoming or anywhere else in the project. Distinct from the already-published ART-006 source ("Article for BECAA Maharashtra Souvenir.docx", a different author). Excluded pending the correct file or an editorial correction of this row. See sprints/v2/MATERIAL_CHANGE_REGISTER.md.</v>
       </c>
     </row>
     <row r="52" ht="22.05" customHeight="1">
       <c r="A52" t="str">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B52" t="str">
-        <v xml:space="preserve">বেঁচে থাকার লড়াই ও স্বপ্নের পথ </v>
+        <v>Chatgpt</v>
       </c>
       <c r="C52" t="str">
-        <v>Article</v>
+        <v>Painting / Drawing</v>
       </c>
       <c r="D52" t="str">
-        <v>Palash Biswas</v>
+        <v>Kallol Roy</v>
       </c>
       <c r="E52" t="str">
-        <v>2006</v>
+        <v>1991</v>
       </c>
       <c r="F52" t="str">
         <v>Civil</v>
       </c>
       <c r="G52" t="str">
-        <v>Palash Article.docx</v>
+        <v>chatgpt kallol.jpeg</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -3027,7 +3027,7 @@
         <v>Approved</v>
       </c>
       <c r="K52" t="str">
-        <v>College Memories</v>
+        <v>Paintings / Drawings</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -3050,59 +3050,163 @@
     </row>
     <row r="53" ht="22.05" customHeight="1">
       <c r="A53" t="str">
+        <v>22</v>
+      </c>
+      <c r="B53" t="str">
+        <v>গোলাপ</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Poem</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Shubhra Basu (wife of Pranab Basu)</v>
+      </c>
+      <c r="E53" t="str">
+        <v>1978</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Shubhra Basu.docx</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Stories / Literature</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v>Sprint v4: revised source received 15.09.2026 (SHA-256 0d068f30b846c0b7eba29f0c16847c4ba3dc90a81733ba8ed23a98c14f328da2) replaces the earlier committed source (SHA-256 83ae8311a1db9205946b5f7f207985eccace7dbf54d771fed3680a9a11d63af9), preserved in 04_MAGAZINE_WORKING/SUPERSEDED_SOURCES/2026-09-15/.</v>
+      </c>
+    </row>
+    <row r="54" ht="22.05" customHeight="1">
+      <c r="A54" t="str">
+        <v>23</v>
+      </c>
+      <c r="B54" t="str">
+        <v xml:space="preserve">বেঁচে থাকার লড়াই ও স্বপ্নের পথ </v>
+      </c>
+      <c r="C54" t="str">
+        <v>Article</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Palash Biswas</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2006</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Palash Article.docx</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K54" t="str">
+        <v>College Memories</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="22.05" customHeight="1">
+      <c r="A55" t="str">
         <v>24</v>
       </c>
-      <c r="B53" t="str">
+      <c r="B55" t="str">
         <v>প্যাঁড়া (Siddhartha Mukhopadhyay story)</v>
       </c>
-      <c r="C53" t="str">
+      <c r="C55" t="str">
         <v>Story</v>
       </c>
-      <c r="D53" t="str">
+      <c r="D55" t="str">
         <v>Siddhartha Mukhopadhyay</v>
       </c>
-      <c r="E53" t="str">
+      <c r="E55" t="str">
         <v>1986</v>
       </c>
-      <c r="F53" t="str">
+      <c r="F55" t="str">
         <v>Electrical</v>
       </c>
-      <c r="G53" t="str">
+      <c r="G55" t="str">
         <v>Siddhartha Mukhopadhyay story.docx</v>
       </c>
-      <c r="H53" t="str">
+      <c r="H55" t="str">
         <v>14.09.2026</v>
       </c>
-      <c r="I53" t="str">
-        <v>Print and web</v>
-      </c>
-      <c r="J53" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="K53" t="str">
+      <c r="I55" t="str">
+        <v>Print and web</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K55" t="str">
         <v>College Memories</v>
       </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
-      <c r="M53" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N53" t="str">
-        <v/>
-      </c>
-      <c r="O53" t="str">
-        <v/>
-      </c>
-      <c r="P53" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q53" t="str">
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q55" t="str">
         <v>Sprint v2: source docx contains only placeholder text ("Story upcoming.") and Permission is still Pending. Excluded until real content and permission are both received. See sprints/v2/MATERIAL_CHANGE_REGISTER.md. Sprint v3: real content received and approval confirmed 2026-09-14; published as ART-012.</v>
       </c>
     </row>
-    <row r="54" ht="22.05" customHeight="1"/>
-    <row r="55" ht="22.05" customHeight="1"/>
     <row r="56" ht="22.05" customHeight="1"/>
     <row r="57" ht="22.05" customHeight="1"/>
     <row r="58" ht="22.05" customHeight="1"/>
@@ -3150,7 +3254,7 @@
     <row r="100" ht="22.05" customHeight="1"/>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q55"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -607,7 +607,7 @@
         <v>Yes</v>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): Bengali spellings "ভাইবই" → "ভাবায়" and "পারিমা" → "পরিমা" in ART-003; original source file unchanged.</v>
       </c>
     </row>
     <row r="7" ht="22.05" customHeight="1">
@@ -660,7 +660,7 @@
         <v>Yes</v>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): reader-facing name shown as "Late Biswajit Sengupta" (manifest display_name, ART-004); Contributor / Company kept as the provenance name.</v>
       </c>
     </row>
     <row r="8" ht="22.05" customHeight="1">
@@ -713,7 +713,7 @@
         <v>Yes</v>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): reader-facing name shown as "Late Biswajit Sengupta" (manifest display_name, ART-005); Contributor / Company kept as the provenance name.</v>
       </c>
     </row>
     <row r="9" ht="22.05" customHeight="1">
@@ -1190,7 +1190,7 @@
         <v>Yes</v>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): published wording "বেকান পরিচয়" → "BECAA-র পরিচয়" in MSG-001; the salutation and বেকানী unchanged; original source file unchanged.</v>
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1">
@@ -1198,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Vice Preseident Desk</v>
+        <v>Vice President Desk</v>
       </c>
       <c r="C18" t="str">
         <v>Article</v>
@@ -1243,7 +1243,7 @@
         <v>Yes</v>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): title spelling "Vice Preseident Desk" → "Vice President Desk" (MSG-002); original source file unchanged.</v>
       </c>
     </row>
     <row r="19" ht="22.05" customHeight="1">

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -395,7 +395,7 @@
         <v>Yes</v>
       </c>
       <c r="Q2" t="str">
-        <v>Unambiguous normalized filename match: 1. Artical Sudip Mazumdar .pdf</v>
+        <v>Unambiguous normalized filename match: 1. Artical Sudip Mazumdar .pdf Sprint v4 2026-09-17 approval (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md, addendum): a stray page-break character (U+000C) removed from the extracted ART-009 text; wording unchanged.</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1">
@@ -660,7 +660,7 @@
         <v>Yes</v>
       </c>
       <c r="Q7" t="str">
-        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): reader-facing name shown as "Late Biswajit Sengupta" (manifest display_name, ART-004); Contributor / Company kept as the provenance name.</v>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): reader-facing name shown as "Late Biswajit Sengupta" (manifest display_name, ART-004); Contributor / Company kept as the provenance name. Sprint v4 2026-09-17 approval (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md, addendum): Bengali author line in the article body changed to "প্রয়াত বিশ্বজিৎ সেনগুপ্ত".</v>
       </c>
     </row>
     <row r="8" ht="22.05" customHeight="1">
@@ -713,7 +713,7 @@
         <v>Yes</v>
       </c>
       <c r="Q8" t="str">
-        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): reader-facing name shown as "Late Biswajit Sengupta" (manifest display_name, ART-005); Contributor / Company kept as the provenance name.</v>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): reader-facing name shown as "Late Biswajit Sengupta" (manifest display_name, ART-005); Contributor / Company kept as the provenance name. Sprint v4 2026-09-17 approval (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md, addendum): Bengali author line in the article body changed to "প্রয়াত বিশ্বজিৎ সেনগুপ্ত".</v>
       </c>
     </row>
     <row r="9" ht="22.05" customHeight="1">
@@ -2780,7 +2780,7 @@
         <v>Yes</v>
       </c>
       <c r="Q47" t="str">
-        <v>Confirmed excluded from website, print and Sponsor Acknowledgements: company name incomplete or unavailable. Sprint v4: re-included as ADV-027, Approved, Sarc Epic — see Notes.</v>
+        <v>Confirmed excluded from website, print and Sponsor Acknowledgements: company name incomplete or unavailable. Sprint v4: re-included as ADV-027, Approved, Sarc Epic — see Notes. Sprint v4 2026-09-17 approval (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md, addendum): the repeated visible heading was removed; the sentence is shown once on the page.</v>
       </c>
     </row>
     <row r="48" ht="22.05" customHeight="1">
@@ -2788,7 +2788,7 @@
         <v>ADV-028</v>
       </c>
       <c r="B48" t="str">
-        <v>Best Compliment from M/s Balajee Infrate</v>
+        <v>We support BECAA Maharashtra for their noble causes. With warm wishes M/s Balajee Infrate</v>
       </c>
       <c r="C48" t="str">
         <v>Advertisement</v>
@@ -2833,7 +2833,7 @@
         <v>Yes</v>
       </c>
       <c r="Q48" t="str">
-        <v>Sprint v4: new text-only advertisement, published as ADV-028.</v>
+        <v>Sprint v4: new text-only advertisement, published as ADV-028. Sprint v4 2026-09-17 approval (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md, addendum): wording changed from "Best Compliment from M/s Balajee Infrate"; shown once on the page.</v>
       </c>
     </row>
     <row r="49" ht="22.05" customHeight="1">
@@ -2886,7 +2886,7 @@
         <v>Yes</v>
       </c>
       <c r="Q49" t="str">
-        <v>Sprint v4: new memorial contribution, published as ADV-029.</v>
+        <v>Sprint v4: new memorial contribution, published as ADV-029. Sprint v4 2026-09-17 approval (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md, addendum): the repeated visible heading was removed; the approved memorial text is shown once.</v>
       </c>
     </row>
     <row r="50" ht="22.05" customHeight="1">

--- a/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
+++ b/04_MAGAZINE_WORKING/BECAA_2026_Content_Tracker.xlsx
@@ -1160,10 +1160,10 @@
         <v>Civil</v>
       </c>
       <c r="G17" t="str">
-        <v>President Desk.docx</v>
+        <v>Souvenir President message 05-09-2026.docx</v>
       </c>
       <c r="H17" t="str">
-        <v>01.08.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="I17" t="str">
         <v>Print and web</v>
@@ -1190,7 +1190,7 @@
         <v>Yes</v>
       </c>
       <c r="Q17" t="str">
-        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): published wording "বেকান পরিচয়" → "BECAA-র পরিচয়" in MSG-001; the salutation and বেকানী unchanged; original source file unchanged.</v>
+        <v>Sprint v4 committee correction (02_INCOMING_CONTENT/BECAA Committee Corrections 2026-09-16.md): published wording "বেকান পরিচয়" → "BECAA-র পরিচয়" in MSG-001; the salutation and বেকানী unchanged; original source file unchanged. Sprint v5 (2026-09-26): message replaced by the President's new English message (Souvenir President message 05-09-2026.docx); old source President Desk.docx archived in 04_MAGAZINE_WORKING/SUPERSEDED_SOURCES/2026-09-26/; the Sprint v4 wording correction applied only to the superseded text and is retired (Decision H).</v>
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1">
@@ -3118,7 +3118,7 @@
         <v>2006</v>
       </c>
       <c r="F54" t="str">
-        <v>Civil</v>
+        <v>Mechanical</v>
       </c>
       <c r="G54" t="str">
         <v>Palash Article.docx</v>
@@ -3151,7 +3151,7 @@
         <v/>
       </c>
       <c r="Q54" t="str">
-        <v/>
+        <v>Sprint v5 (2026-09-26): branch corrected Civil → Mechanical at the owner's request (BECAA Owner Corrections 2026-09-26.md); byline now "Palash Biswas, Mechanical, 2006 Batch".</v>
       </c>
     </row>
     <row r="55" ht="22.05" customHeight="1">
